--- a/diseases/d097/2015-2019.xlsx
+++ b/diseases/d097/2015-2019.xlsx
@@ -2741,6 +2741,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2889,6 +2894,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3037,6 +3047,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3185,6 +3200,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3333,6 +3353,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3481,6 +3506,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3629,6 +3659,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3777,6 +3812,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3925,6 +3965,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4073,6 +4118,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4221,6 +4271,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4369,6 +4424,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4517,6 +4577,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4665,6 +4730,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4813,6 +4883,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4961,6 +5036,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5109,6 +5189,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5257,6 +5342,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5405,6 +5495,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5553,6 +5648,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5701,6 +5801,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5849,6 +5954,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5997,6 +6107,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6145,6 +6260,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6293,6 +6413,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6441,6 +6566,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6589,6 +6719,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6737,6 +6872,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6885,6 +7025,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7033,6 +7178,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7181,6 +7331,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7329,6 +7484,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7477,6 +7637,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7625,6 +7790,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7773,6 +7943,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7921,6 +8096,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8069,6 +8249,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8215,6 +8400,11 @@
       <c r="S49" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">

--- a/diseases/d097/2015-2019.xlsx
+++ b/diseases/d097/2015-2019.xlsx
@@ -13923,11 +13923,6 @@
       <c r="P89" t="n">
         <v>1</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U89" t="inlineStr">
         <is>
           <t>HOLD_US_31b2a115e176e0fae5fc063fe6d1</t>
@@ -13945,12 +13940,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ89" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
@@ -13960,11 +13950,6 @@
       </c>
       <c r="AT89" t="n">
         <v>1</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -14030,17 +14015,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>US-DE</t>
+          <t>US-GA</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Delaware, United States</t>
+          <t>Georgia, United States</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -14074,102 +14059,24 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
           <t>HOLD_US_31b2a115e176e0fae5fc063fe6d1</t>
         </is>
       </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Cyclosporiasis</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>Cyclosporiasis</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>country:US-DE:national</t>
-        </is>
-      </c>
-      <c r="AD90" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE90" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF90" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG90" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN90" t="b">
-        <v>1</v>
-      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -14177,12 +14084,7 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
@@ -14192,11 +14094,6 @@
       </c>
       <c r="AT90" t="n">
         <v>1</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -14267,12 +14164,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>US-GA</t>
+          <t>US-IA</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Georgia, United States</t>
+          <t>Iowa, United States</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -14411,12 +14308,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>US-IA</t>
+          <t>US-LA</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Iowa, United States</t>
+          <t>Louisiana, United States</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -14450,13 +14347,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
@@ -14555,12 +14452,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>US-LA</t>
+          <t>US-MA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Louisiana, United States</t>
+          <t>Massachusetts, United States</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -14594,13 +14491,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O93" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P93" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -14699,12 +14596,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>US-MA</t>
+          <t>US-MD</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Massachusetts, United States</t>
+          <t>Maryland, United States</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -14738,13 +14635,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
@@ -14843,12 +14740,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>US-MD</t>
+          <t>US-MO</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Maryland, United States</t>
+          <t>Missouri, United States</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -14882,13 +14779,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O95" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P95" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -14987,12 +14884,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>US-MO</t>
+          <t>US-NE</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Missouri, United States</t>
+          <t>Nebraska, United States</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -15026,13 +14923,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
@@ -15131,12 +15028,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>US-NE</t>
+          <t>US-NM</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nebraska, United States</t>
+          <t>New Mexico, United States</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -15170,13 +15067,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -15275,12 +15172,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>US-NM</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>New Mexico, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -15314,13 +15211,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O98" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P98" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
@@ -15419,12 +15316,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US-OH</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>Ohio, United States</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -15563,12 +15460,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>US-OH</t>
+          <t>US-RI</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ohio, United States</t>
+          <t>Rhode Island, United States</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -15602,13 +15499,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="O100" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P100" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -15707,12 +15604,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>US-RI</t>
+          <t>US-TX</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Rhode Island, United States</t>
+          <t>Texas, United States</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -15746,13 +15643,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O101" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P101" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -15851,12 +15748,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>US-TX</t>
+          <t>US-VA</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Texas, United States</t>
+          <t>Virginia, United States</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -15890,13 +15787,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="O102" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="P102" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -15995,12 +15892,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>US-VA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Virginia, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -16025,7 +15922,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2019-07-13</t>
+          <t>2019-07-20</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -16034,13 +15931,19 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>6</v>
+        <v>262</v>
       </c>
       <c r="O103" t="n">
-        <v>6</v>
+        <v>262</v>
       </c>
       <c r="P103" t="n">
-        <v>6</v>
+        <v>262</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0.07756296764872452</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -16054,7 +15957,7 @@
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
@@ -16082,32 +15985,32 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -16139,12 +16042,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-AR</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Arkansas, United States</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -16178,19 +16081,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>262</v>
+        <v>1</v>
       </c>
       <c r="O104" t="n">
-        <v>262</v>
+        <v>1</v>
       </c>
       <c r="P104" t="n">
-        <v>262</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
-      <c r="R104" t="n">
-        <v>0.07756296764872452</v>
+        <v>1</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
@@ -16204,7 +16101,7 @@
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
@@ -16232,32 +16129,32 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16289,12 +16186,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>US-AR</t>
+          <t>US-AZ</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Arkansas, United States</t>
+          <t>Arizona, United States</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -16328,13 +16225,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -16433,12 +16330,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>US-AZ</t>
+          <t>US-CO</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Arizona, United States</t>
+          <t>Colorado, United States</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -16472,13 +16369,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O106" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P106" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U106" t="inlineStr">
         <is>
@@ -16577,12 +16474,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>US-CO</t>
+          <t>US-FL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Colorado, United States</t>
+          <t>Florida, United States</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -16616,13 +16513,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="O107" t="n">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="P107" t="n">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
@@ -16721,12 +16618,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>US-FL</t>
+          <t>US-GA</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Florida, United States</t>
+          <t>Georgia, United States</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -16760,13 +16657,13 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="O108" t="n">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="P108" t="n">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="U108" t="inlineStr">
         <is>
@@ -16865,12 +16762,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>US-GA</t>
+          <t>US-MA</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Georgia, United States</t>
+          <t>Massachusetts, United States</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -16904,13 +16801,13 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O109" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P109" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
@@ -17009,12 +16906,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>US-MA</t>
+          <t>US-MD</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Massachusetts, United States</t>
+          <t>Maryland, United States</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -17048,13 +16945,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="O110" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="P110" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="U110" t="inlineStr">
         <is>
@@ -17153,12 +17050,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>US-MD</t>
+          <t>US-MO</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Maryland, United States</t>
+          <t>Missouri, United States</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -17192,13 +17089,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="O111" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="P111" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
@@ -17297,12 +17194,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>US-MO</t>
+          <t>US-NE</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Missouri, United States</t>
+          <t>Nebraska, United States</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -17336,13 +17233,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O112" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P112" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
@@ -17441,12 +17338,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>US-NE</t>
+          <t>US-NM</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nebraska, United States</t>
+          <t>New Mexico, United States</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -17480,13 +17377,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O113" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P113" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
@@ -17585,12 +17482,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>US-NM</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>New Mexico, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -17624,13 +17521,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="O114" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="P114" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
@@ -17729,12 +17626,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US-OH</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>Ohio, United States</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -17768,13 +17665,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="O115" t="n">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="P115" t="n">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
@@ -17873,12 +17770,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>US-OH</t>
+          <t>US-TX</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ohio, United States</t>
+          <t>Texas, United States</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -17912,13 +17809,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="O116" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="P116" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
@@ -18017,12 +17914,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>US-TX</t>
+          <t>US-VA</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Texas, United States</t>
+          <t>Virginia, United States</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -18056,13 +17953,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O117" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P117" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
@@ -18161,12 +18058,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>US-VA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Virginia, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -18191,7 +18088,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2019-07-20</t>
+          <t>2019-07-27</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -18200,13 +18097,19 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>14</v>
+        <v>186</v>
       </c>
       <c r="O118" t="n">
-        <v>14</v>
+        <v>186</v>
       </c>
       <c r="P118" t="n">
-        <v>14</v>
+        <v>186</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.05506378619336931</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
@@ -18220,7 +18123,7 @@
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
@@ -18248,32 +18151,32 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -18305,12 +18208,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-AR</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Arkansas, United States</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -18344,19 +18247,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>186</v>
+        <v>2</v>
       </c>
       <c r="O119" t="n">
-        <v>186</v>
+        <v>2</v>
       </c>
       <c r="P119" t="n">
-        <v>186</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
-      <c r="R119" t="n">
-        <v>0.05506378619336931</v>
+        <v>2</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
@@ -18370,7 +18267,7 @@
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
@@ -18398,32 +18295,32 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18455,12 +18352,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>US-AR</t>
+          <t>US-AZ</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Arkansas, United States</t>
+          <t>Arizona, United States</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -18494,13 +18391,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O120" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P120" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
@@ -18599,12 +18496,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>US-AZ</t>
+          <t>US-CO</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Arizona, United States</t>
+          <t>Colorado, United States</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -18638,13 +18535,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O121" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P121" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
@@ -18743,12 +18640,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>US-CO</t>
+          <t>US-CT</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Colorado, United States</t>
+          <t>Connecticut, United States</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -18782,13 +18679,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
@@ -18887,12 +18784,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>US-CT</t>
+          <t>US-FL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Connecticut, United States</t>
+          <t>Florida, United States</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -18926,13 +18823,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O123" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P123" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U123" t="inlineStr">
         <is>
@@ -19031,12 +18928,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>US-FL</t>
+          <t>US-GA</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Florida, United States</t>
+          <t>Georgia, United States</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -19070,13 +18967,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O124" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P124" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
@@ -19175,12 +19072,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>US-GA</t>
+          <t>US-MA</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Georgia, United States</t>
+          <t>Massachusetts, United States</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -19214,13 +19111,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O125" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P125" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
@@ -19319,12 +19216,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>US-MA</t>
+          <t>US-MD</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Massachusetts, United States</t>
+          <t>Maryland, United States</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -19358,13 +19255,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="O126" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="P126" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="U126" t="inlineStr">
         <is>
@@ -19463,12 +19360,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>US-MD</t>
+          <t>US-MO</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Maryland, United States</t>
+          <t>Missouri, United States</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -19502,13 +19399,13 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O127" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="P127" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
@@ -19607,12 +19504,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>US-MO</t>
+          <t>US-NE</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Missouri, United States</t>
+          <t>Nebraska, United States</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -19646,13 +19543,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O128" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P128" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U128" t="inlineStr">
         <is>
@@ -19751,12 +19648,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>US-NE</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Nebraska, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -19790,13 +19687,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="O129" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="P129" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
@@ -19895,12 +19792,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US-OH</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>Ohio, United States</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -19934,13 +19831,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="O130" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="P130" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="U130" t="inlineStr">
         <is>
@@ -20039,12 +19936,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>US-OH</t>
+          <t>US-OR</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ohio, United States</t>
+          <t>Oregon, United States</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -20078,13 +19975,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O131" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P131" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U131" t="inlineStr">
         <is>
@@ -20183,12 +20080,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>US-OR</t>
+          <t>US-RI</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Oregon, United States</t>
+          <t>Rhode Island, United States</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -20222,13 +20119,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
@@ -20327,12 +20224,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>US-RI</t>
+          <t>US-SC</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Rhode Island, United States</t>
+          <t>South Carolina, United States</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -20471,12 +20368,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>US-SC</t>
+          <t>US-TN</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>South Carolina, United States</t>
+          <t>Tennessee, United States</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -20615,12 +20512,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>US-TN</t>
+          <t>US-TX</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tennessee, United States</t>
+          <t>Texas, United States</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -20654,13 +20551,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O135" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P135" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
@@ -20759,12 +20656,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>US-TX</t>
+          <t>US-VA</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Texas, United States</t>
+          <t>Virginia, United States</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -20798,13 +20695,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="O136" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="P136" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="U136" t="inlineStr">
         <is>
@@ -20903,12 +20800,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>US-VA</t>
+          <t>US-WI</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Virginia, United States</t>
+          <t>Wisconsin, United States</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -20942,13 +20839,13 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="O137" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="P137" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
@@ -21047,12 +20944,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>US-WI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Wisconsin, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -21077,22 +20974,28 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2019-07-27</t>
+          <t>2019-08-03</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2019-07</t>
+          <t>2019-08</t>
         </is>
       </c>
       <c r="N138" t="n">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="O138" t="n">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="P138" t="n">
-        <v>4</v>
+        <v>179</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.05299149316458659</v>
       </c>
       <c r="U138" t="inlineStr">
         <is>
@@ -21106,7 +21009,7 @@
       </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
@@ -21134,32 +21037,32 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21191,12 +21094,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-AR</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Arkansas, United States</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -21230,19 +21133,13 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>179</v>
+        <v>4</v>
       </c>
       <c r="O139" t="n">
-        <v>179</v>
+        <v>4</v>
       </c>
       <c r="P139" t="n">
-        <v>179</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0.05299149316458659</v>
+        <v>4</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
@@ -21256,7 +21153,7 @@
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
@@ -21284,32 +21181,32 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21341,12 +21238,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>US-AR</t>
+          <t>US-CO</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Arkansas, United States</t>
+          <t>Colorado, United States</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -21380,13 +21277,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O140" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P140" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U140" t="inlineStr">
         <is>
@@ -21485,12 +21382,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>US-CO</t>
+          <t>US-LA</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Colorado, United States</t>
+          <t>Louisiana, United States</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -21524,13 +21421,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
@@ -21629,12 +21526,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>US-LA</t>
+          <t>US-MA</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Louisiana, United States</t>
+          <t>Massachusetts, United States</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -21668,13 +21565,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O142" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P142" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U142" t="inlineStr">
         <is>
@@ -21773,12 +21670,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>US-MA</t>
+          <t>US-MD</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Massachusetts, United States</t>
+          <t>Maryland, United States</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -21812,13 +21709,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="O143" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="P143" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
@@ -21917,12 +21814,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>US-MD</t>
+          <t>US-MO</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Maryland, United States</t>
+          <t>Missouri, United States</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -21956,13 +21853,13 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="O144" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="P144" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="U144" t="inlineStr">
         <is>
@@ -22061,12 +21958,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>US-MO</t>
+          <t>US-NE</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Missouri, United States</t>
+          <t>Nebraska, United States</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -22205,12 +22102,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>US-NE</t>
+          <t>US-NJ</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Nebraska, United States</t>
+          <t>New Jersey, United States</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -22244,13 +22141,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O146" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P146" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U146" t="inlineStr">
         <is>
@@ -22349,12 +22246,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>US-NJ</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>New Jersey, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -22388,13 +22285,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="O147" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="P147" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
@@ -22493,12 +22390,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US-OH</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>Ohio, United States</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -22532,13 +22429,13 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O148" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P148" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="U148" t="inlineStr">
         <is>
@@ -22637,12 +22534,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>US-OH</t>
+          <t>US-RI</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ohio, United States</t>
+          <t>Rhode Island, United States</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -22676,13 +22573,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="O149" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="P149" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="U149" t="inlineStr">
         <is>
@@ -22781,12 +22678,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>US-RI</t>
+          <t>US-SC</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Rhode Island, United States</t>
+          <t>South Carolina, United States</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -22820,13 +22717,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U150" t="inlineStr">
         <is>
@@ -22925,12 +22822,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>US-SC</t>
+          <t>US-TX</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>South Carolina, United States</t>
+          <t>Texas, United States</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -22964,13 +22861,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O151" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P151" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U151" t="inlineStr">
         <is>
@@ -23069,12 +22966,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>US-TX</t>
+          <t>US-VA</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Texas, United States</t>
+          <t>Virginia, United States</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -23108,13 +23005,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="O152" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="P152" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="U152" t="inlineStr">
         <is>
@@ -23213,12 +23110,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>US-VA</t>
+          <t>US-WI</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Virginia, United States</t>
+          <t>Wisconsin, United States</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -23252,13 +23149,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="O153" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="P153" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
@@ -23357,12 +23254,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>US-WI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Wisconsin, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -23387,7 +23284,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2019-08-03</t>
+          <t>2019-08-10</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -23396,13 +23293,19 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="O154" t="n">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="P154" t="n">
-        <v>3</v>
+        <v>84</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0.02486751634539259</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
@@ -23416,7 +23319,7 @@
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
@@ -23444,32 +23347,32 @@
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23501,12 +23404,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-AR</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Arkansas, United States</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -23540,19 +23443,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>84</v>
+        <v>2</v>
       </c>
       <c r="O155" t="n">
-        <v>84</v>
+        <v>2</v>
       </c>
       <c r="P155" t="n">
-        <v>84</v>
-      </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
-      <c r="R155" t="n">
-        <v>0.02486751634539259</v>
+        <v>2</v>
       </c>
       <c r="U155" t="inlineStr">
         <is>
@@ -23566,7 +23463,7 @@
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
@@ -23594,32 +23491,32 @@
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23651,12 +23548,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>US-AR</t>
+          <t>US-CT</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Arkansas, United States</t>
+          <t>Connecticut, United States</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -23690,13 +23587,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U156" t="inlineStr">
         <is>
@@ -23795,12 +23692,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>US-CT</t>
+          <t>US-GA</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Connecticut, United States</t>
+          <t>Georgia, United States</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -23834,13 +23731,13 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
@@ -23939,12 +23836,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>US-GA</t>
+          <t>US-MA</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Georgia, United States</t>
+          <t>Massachusetts, United States</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -24083,12 +23980,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>US-MA</t>
+          <t>US-MD</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Massachusetts, United States</t>
+          <t>Maryland, United States</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -24122,13 +24019,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O159" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="P159" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="U159" t="inlineStr">
         <is>
@@ -24227,12 +24124,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>US-MD</t>
+          <t>US-MO</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Maryland, United States</t>
+          <t>Missouri, United States</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -24266,13 +24163,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O160" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="P160" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="U160" t="inlineStr">
         <is>
@@ -24371,12 +24268,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>US-MO</t>
+          <t>US-NE</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Missouri, United States</t>
+          <t>Nebraska, United States</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -24410,13 +24307,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U161" t="inlineStr">
         <is>
@@ -24515,12 +24412,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>US-NE</t>
+          <t>US-NJ</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Nebraska, United States</t>
+          <t>New Jersey, United States</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -24554,13 +24451,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U162" t="inlineStr">
         <is>
@@ -24659,12 +24556,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>US-NJ</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>New Jersey, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -24698,13 +24595,13 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="O163" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="P163" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="U163" t="inlineStr">
         <is>
@@ -24803,12 +24700,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US-OH</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>Ohio, United States</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -24842,13 +24739,13 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O164" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="P164" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="U164" t="inlineStr">
         <is>
@@ -24947,12 +24844,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>US-OH</t>
+          <t>US-RI</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Ohio, United States</t>
+          <t>Rhode Island, United States</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -25091,12 +24988,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>US-RI</t>
+          <t>US-SC</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Rhode Island, United States</t>
+          <t>South Carolina, United States</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -25130,13 +25027,13 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O166" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P166" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U166" t="inlineStr">
         <is>
@@ -25235,12 +25132,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>US-SC</t>
+          <t>US-TN</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>South Carolina, United States</t>
+          <t>Tennessee, United States</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -25379,12 +25276,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>US-TN</t>
+          <t>US-VA</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Tennessee, United States</t>
+          <t>Virginia, United States</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -25418,13 +25315,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="O168" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="P168" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="U168" t="inlineStr">
         <is>
@@ -25523,12 +25420,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>US-VA</t>
+          <t>US-WI</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Virginia, United States</t>
+          <t>Wisconsin, United States</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -25562,13 +25459,13 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="O169" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="P169" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="U169" t="inlineStr">
         <is>
@@ -25667,12 +25564,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>US-WI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Wisconsin, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -25697,7 +25594,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2019-08-10</t>
+          <t>2019-08-17</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -25706,13 +25603,19 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="O170" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="P170" t="n">
-        <v>2</v>
+        <v>70</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>0</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0.02072293028782716</v>
       </c>
       <c r="U170" t="inlineStr">
         <is>
@@ -25726,7 +25629,7 @@
       </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
@@ -25754,32 +25657,32 @@
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25811,12 +25714,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-AR</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Arkansas, United States</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -25850,19 +25753,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="O171" t="n">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="P171" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
-      <c r="R171" t="n">
-        <v>0.02072293028782716</v>
+        <v>7</v>
       </c>
       <c r="U171" t="inlineStr">
         <is>
@@ -25876,7 +25773,7 @@
       </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
@@ -25904,32 +25801,32 @@
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25961,12 +25858,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>US-AR</t>
+          <t>US-AZ</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Arkansas, United States</t>
+          <t>Arizona, United States</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -26000,13 +25897,13 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O172" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P172" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="U172" t="inlineStr">
         <is>
@@ -26105,12 +26002,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>US-AZ</t>
+          <t>US-CT</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Arizona, United States</t>
+          <t>Connecticut, United States</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -26249,12 +26146,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>US-CT</t>
+          <t>US-GA</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Connecticut, United States</t>
+          <t>Georgia, United States</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -26288,13 +26185,13 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O174" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P174" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U174" t="inlineStr">
         <is>
@@ -26393,12 +26290,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>US-GA</t>
+          <t>US-LA</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Georgia, United States</t>
+          <t>Louisiana, United States</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -26432,13 +26329,13 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O175" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P175" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U175" t="inlineStr">
         <is>
@@ -26537,12 +26434,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>US-LA</t>
+          <t>US-MA</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Louisiana, United States</t>
+          <t>Massachusetts, United States</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -26576,13 +26473,13 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O176" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P176" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U176" t="inlineStr">
         <is>
@@ -26681,12 +26578,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>US-MA</t>
+          <t>US-MD</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Massachusetts, United States</t>
+          <t>Maryland, United States</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -26825,12 +26722,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>US-MD</t>
+          <t>US-MO</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Maryland, United States</t>
+          <t>Missouri, United States</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -26969,12 +26866,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>US-MO</t>
+          <t>US-NE</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Missouri, United States</t>
+          <t>Nebraska, United States</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -27008,13 +26905,13 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U179" t="inlineStr">
         <is>
@@ -27113,12 +27010,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>US-NE</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Nebraska, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -27152,13 +27049,13 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O180" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="P180" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U180" t="inlineStr">
         <is>
@@ -27257,12 +27154,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US-OH</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>Ohio, United States</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -27296,13 +27193,13 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="O181" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="P181" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="U181" t="inlineStr">
         <is>
@@ -27401,12 +27298,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>US-OH</t>
+          <t>US-TX</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Ohio, United States</t>
+          <t>Texas, United States</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -27440,13 +27337,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O182" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="P182" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="U182" t="inlineStr">
         <is>
@@ -27545,12 +27442,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>US-TX</t>
+          <t>US-VA</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Texas, United States</t>
+          <t>Virginia, United States</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -27584,13 +27481,13 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="O183" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="P183" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="U183" t="inlineStr">
         <is>
@@ -27689,12 +27586,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>US-VA</t>
+          <t>US-WI</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Virginia, United States</t>
+          <t>Wisconsin, United States</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -27728,13 +27625,13 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="O184" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="P184" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="U184" t="inlineStr">
         <is>
@@ -27833,12 +27730,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>US-WI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Wisconsin, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -27863,7 +27760,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2019-08-17</t>
+          <t>2019-08-24</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -27872,13 +27769,19 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="O185" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="P185" t="n">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>0</v>
+      </c>
+      <c r="R185" t="n">
+        <v>0.02871606054170335</v>
       </c>
       <c r="U185" t="inlineStr">
         <is>
@@ -27892,7 +27795,7 @@
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
@@ -27920,32 +27823,32 @@
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27977,12 +27880,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-AR</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Arkansas, United States</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -28016,19 +27919,13 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>97</v>
+        <v>4</v>
       </c>
       <c r="O186" t="n">
-        <v>97</v>
+        <v>4</v>
       </c>
       <c r="P186" t="n">
-        <v>97</v>
-      </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
-      <c r="R186" t="n">
-        <v>0.02871606054170335</v>
+        <v>4</v>
       </c>
       <c r="U186" t="inlineStr">
         <is>
@@ -28042,7 +27939,7 @@
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
@@ -28070,32 +27967,32 @@
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28127,12 +28024,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>US-AR</t>
+          <t>US-FL</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Arkansas, United States</t>
+          <t>Florida, United States</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -28166,13 +28063,13 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="O187" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="P187" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="U187" t="inlineStr">
         <is>
@@ -28271,12 +28168,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>US-FL</t>
+          <t>US-GA</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Florida, United States</t>
+          <t>Georgia, United States</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -28310,13 +28207,13 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="O188" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="P188" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="U188" t="inlineStr">
         <is>
@@ -28415,12 +28312,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>US-GA</t>
+          <t>US-LA</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Georgia, United States</t>
+          <t>Louisiana, United States</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -28454,13 +28351,13 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U189" t="inlineStr">
         <is>
@@ -28559,12 +28456,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>US-LA</t>
+          <t>US-MA</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Louisiana, United States</t>
+          <t>Massachusetts, United States</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -28598,13 +28495,13 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U190" t="inlineStr">
         <is>
@@ -28703,12 +28600,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>US-MA</t>
+          <t>US-MD</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Massachusetts, United States</t>
+          <t>Maryland, United States</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -28742,13 +28639,13 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O191" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P191" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U191" t="inlineStr">
         <is>
@@ -28847,12 +28744,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>US-MD</t>
+          <t>US-MO</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Maryland, United States</t>
+          <t>Missouri, United States</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -28886,13 +28783,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O192" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P192" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U192" t="inlineStr">
         <is>
@@ -28991,12 +28888,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>US-MO</t>
+          <t>US-NE</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Missouri, United States</t>
+          <t>Nebraska, United States</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -29030,13 +28927,13 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U193" t="inlineStr">
         <is>
@@ -29135,12 +29032,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>US-NE</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Nebraska, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -29279,12 +29176,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US-OH</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>Ohio, United States</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -29318,13 +29215,13 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O195" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P195" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U195" t="inlineStr">
         <is>
@@ -29423,12 +29320,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>US-OH</t>
+          <t>US-TX</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Ohio, United States</t>
+          <t>Texas, United States</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -29462,13 +29359,13 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="O196" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="P196" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="U196" t="inlineStr">
         <is>
@@ -29567,12 +29464,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>US-TX</t>
+          <t>US-VA</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Texas, United States</t>
+          <t>Virginia, United States</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -29606,13 +29503,13 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="O197" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="P197" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="U197" t="inlineStr">
         <is>
@@ -29711,12 +29608,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>US-VA</t>
+          <t>US-WI</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Virginia, United States</t>
+          <t>Wisconsin, United States</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -29750,13 +29647,13 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O198" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P198" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U198" t="inlineStr">
         <is>
@@ -29855,12 +29752,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>US-WI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Wisconsin, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -29885,7 +29782,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2019-08-24</t>
+          <t>2019-08-31</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -29894,13 +29791,19 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="O199" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="P199" t="n">
-        <v>1</v>
+        <v>31</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>0</v>
+      </c>
+      <c r="R199" t="n">
+        <v>0.009177297698894884</v>
       </c>
       <c r="U199" t="inlineStr">
         <is>
@@ -29914,7 +29817,7 @@
       </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
@@ -29942,32 +29845,32 @@
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29999,12 +29902,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-AR</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Arkansas, United States</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -30038,19 +29941,13 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="O200" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="P200" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
-      <c r="R200" t="n">
-        <v>0.009177297698894884</v>
+        <v>2</v>
       </c>
       <c r="U200" t="inlineStr">
         <is>
@@ -30064,7 +29961,7 @@
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
@@ -30092,32 +29989,32 @@
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30149,12 +30046,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>US-AR</t>
+          <t>US-CO</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Arkansas, United States</t>
+          <t>Colorado, United States</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -30293,12 +30190,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>US-CO</t>
+          <t>US-FL</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Colorado, United States</t>
+          <t>Florida, United States</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -30332,13 +30229,13 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O202" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P202" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U202" t="inlineStr">
         <is>
@@ -30437,12 +30334,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>US-FL</t>
+          <t>US-LA</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Florida, United States</t>
+          <t>Louisiana, United States</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -30476,13 +30373,13 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O203" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P203" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U203" t="inlineStr">
         <is>
@@ -30581,12 +30478,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>US-LA</t>
+          <t>US-MD</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Louisiana, United States</t>
+          <t>Maryland, United States</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -30620,13 +30517,13 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O204" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P204" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U204" t="inlineStr">
         <is>
@@ -30725,12 +30622,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>US-MD</t>
+          <t>US-MO</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Maryland, United States</t>
+          <t>Missouri, United States</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -30869,12 +30766,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>US-MO</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Missouri, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -30908,13 +30805,13 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O206" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P206" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U206" t="inlineStr">
         <is>
@@ -31013,12 +30910,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US-OH</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>Ohio, United States</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -31052,13 +30949,13 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O207" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P207" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U207" t="inlineStr">
         <is>
@@ -31157,12 +31054,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>US-OH</t>
+          <t>US-SC</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Ohio, United States</t>
+          <t>South Carolina, United States</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -31301,12 +31198,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>US-SC</t>
+          <t>US-TX</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>South Carolina, United States</t>
+          <t>Texas, United States</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -31340,13 +31237,13 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O209" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P209" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U209" t="inlineStr">
         <is>
@@ -31445,12 +31342,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>US-TX</t>
+          <t>US-VA</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Texas, United States</t>
+          <t>Virginia, United States</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -31484,13 +31381,13 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O210" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="P210" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U210" t="inlineStr">
         <is>
@@ -31589,12 +31486,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>US-VA</t>
+          <t>US-WI</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Virginia, United States</t>
+          <t>Wisconsin, United States</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -31628,13 +31525,13 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O211" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P211" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U211" t="inlineStr">
         <is>
@@ -31733,12 +31630,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>US-WI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Wisconsin, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -31763,22 +31660,28 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2019-08-31</t>
+          <t>2019-09-07</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>2019-08</t>
+          <t>2019-09</t>
         </is>
       </c>
       <c r="N212" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="O212" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="P212" t="n">
-        <v>1</v>
+        <v>36</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>0</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0.01065750700516825</v>
       </c>
       <c r="U212" t="inlineStr">
         <is>
@@ -31792,7 +31695,7 @@
       </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
@@ -31820,32 +31723,32 @@
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -31877,12 +31780,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-AR</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Arkansas, United States</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -31916,19 +31819,13 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="O213" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="P213" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
-      <c r="R213" t="n">
-        <v>0.01065750700516825</v>
+        <v>1</v>
       </c>
       <c r="U213" t="inlineStr">
         <is>
@@ -31942,7 +31839,7 @@
       </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
@@ -31970,32 +31867,32 @@
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32027,12 +31924,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>US-AR</t>
+          <t>US-AZ</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Arkansas, United States</t>
+          <t>Arizona, United States</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -32171,12 +32068,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>US-AZ</t>
+          <t>US-CA</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Arizona, United States</t>
+          <t>California, United States</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -32315,12 +32212,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>US-CA</t>
+          <t>US-MD</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>California, United States</t>
+          <t>Maryland, United States</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -32354,13 +32251,13 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U216" t="inlineStr">
         <is>
@@ -32459,12 +32356,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>US-MD</t>
+          <t>US-TX</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Maryland, United States</t>
+          <t>Texas, United States</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -32498,13 +32395,13 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="O217" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="P217" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="U217" t="inlineStr">
         <is>
@@ -32603,12 +32500,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>US-TX</t>
+          <t>US-WI</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Texas, United States</t>
+          <t>Wisconsin, United States</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -32642,13 +32539,13 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="O218" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="P218" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="U218" t="inlineStr">
         <is>
@@ -32747,12 +32644,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>US-WI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Wisconsin, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -32777,7 +32674,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2019-09-07</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -32786,13 +32683,19 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="O219" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="P219" t="n">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>0</v>
+      </c>
+      <c r="R219" t="n">
+        <v>0.00473666978007478</v>
       </c>
       <c r="U219" t="inlineStr">
         <is>
@@ -32806,7 +32709,7 @@
       </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP219" t="inlineStr">
@@ -32834,32 +32737,32 @@
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -32891,12 +32794,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-AR</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Arkansas, United States</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -32930,19 +32833,13 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="O220" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="P220" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
-      <c r="R220" t="n">
-        <v>0.00473666978007478</v>
+        <v>3</v>
       </c>
       <c r="U220" t="inlineStr">
         <is>
@@ -32956,7 +32853,7 @@
       </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
@@ -32984,32 +32881,32 @@
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33041,12 +32938,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>US-AR</t>
+          <t>US-AZ</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Arkansas, United States</t>
+          <t>Arizona, United States</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -33080,13 +32977,13 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O221" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P221" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U221" t="inlineStr">
         <is>
@@ -33185,12 +33082,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>US-AZ</t>
+          <t>US-FL</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Arizona, United States</t>
+          <t>Florida, United States</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -33224,13 +33121,13 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O222" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P222" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U222" t="inlineStr">
         <is>
@@ -33329,12 +33226,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>US-FL</t>
+          <t>US-MD</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Florida, United States</t>
+          <t>Maryland, United States</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -33368,13 +33265,13 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O223" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P223" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U223" t="inlineStr">
         <is>
@@ -33473,12 +33370,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>US-MD</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Maryland, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -33512,13 +33409,13 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O224" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P224" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U224" t="inlineStr">
         <is>
@@ -33617,12 +33514,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US-TX</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>Texas, United States</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -33656,13 +33553,13 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O225" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P225" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U225" t="inlineStr">
         <is>
@@ -33761,12 +33658,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>US-TX</t>
+          <t>US-WI</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Texas, United States</t>
+          <t>Wisconsin, United States</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -33800,13 +33697,13 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U226" t="inlineStr">
         <is>
@@ -33905,12 +33802,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>US-WI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Wisconsin, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -33935,7 +33832,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
+          <t>2019-09-21</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -33944,13 +33841,19 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="O227" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="P227" t="n">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>0</v>
+      </c>
+      <c r="R227" t="n">
+        <v>0.005328753502584127</v>
       </c>
       <c r="U227" t="inlineStr">
         <is>
@@ -33964,7 +33867,7 @@
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
@@ -33992,32 +33895,32 @@
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -34049,12 +33952,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-MD</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Maryland, United States</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -34088,19 +33991,13 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="O228" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="P228" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
-      <c r="R228" t="n">
-        <v>0.005328753502584127</v>
+        <v>1</v>
       </c>
       <c r="U228" t="inlineStr">
         <is>
@@ -34114,7 +34011,7 @@
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
@@ -34142,32 +34039,32 @@
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34199,12 +34096,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>US-MD</t>
+          <t>US-TX</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Maryland, United States</t>
+          <t>Texas, United States</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -34238,13 +34135,13 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="O229" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="P229" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U229" t="inlineStr">
         <is>
@@ -34343,12 +34240,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>US-TX</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Texas, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -34373,7 +34270,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
+          <t>2019-09-28</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -34382,13 +34279,19 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="O230" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="P230" t="n">
-        <v>17</v>
+        <v>8</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>0</v>
+      </c>
+      <c r="R230" t="n">
+        <v>0.00236833489003739</v>
       </c>
       <c r="U230" t="inlineStr">
         <is>
@@ -34402,7 +34305,7 @@
       </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
@@ -34430,32 +34333,32 @@
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -34487,12 +34390,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-AR</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Arkansas, United States</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -34526,19 +34429,13 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O231" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P231" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
-      <c r="R231" t="n">
-        <v>0.00236833489003739</v>
+        <v>1</v>
       </c>
       <c r="U231" t="inlineStr">
         <is>
@@ -34552,7 +34449,7 @@
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
@@ -34580,32 +34477,32 @@
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34637,12 +34534,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>US-AR</t>
+          <t>US-MO</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Arkansas, United States</t>
+          <t>Missouri, United States</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -34781,12 +34678,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>US-MO</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Missouri, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -34820,13 +34717,13 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O233" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P233" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U233" t="inlineStr">
         <is>
@@ -34925,12 +34822,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US-VA</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>Virginia, United States</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -34964,13 +34861,13 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O234" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P234" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U234" t="inlineStr">
         <is>
@@ -35069,12 +34966,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>US-VA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Virginia, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -35099,22 +34996,28 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2019-09-28</t>
+          <t>2019-10-05</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>2019-09</t>
+          <t>2019-10</t>
         </is>
       </c>
       <c r="N235" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O235" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P235" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>0</v>
+      </c>
+      <c r="R235" t="n">
+        <v>0.001480209306273368</v>
       </c>
       <c r="U235" t="inlineStr">
         <is>
@@ -35128,7 +35031,7 @@
       </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
@@ -35156,32 +35059,32 @@
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35213,12 +35116,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-AZ</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Arizona, United States</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -35252,19 +35155,13 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O236" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P236" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
-      <c r="R236" t="n">
-        <v>0.001480209306273368</v>
+        <v>1</v>
       </c>
       <c r="U236" t="inlineStr">
         <is>
@@ -35278,7 +35175,7 @@
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
@@ -35306,32 +35203,32 @@
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35363,12 +35260,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>US-AZ</t>
+          <t>US-MD</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Arizona, United States</t>
+          <t>Maryland, United States</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -35507,12 +35404,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>US-MD</t>
+          <t>US-TX</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Maryland, United States</t>
+          <t>Texas, United States</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -35651,12 +35548,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>US-TX</t>
+          <t>US-VA</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Texas, United States</t>
+          <t>Virginia, United States</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -35690,13 +35587,13 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O239" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P239" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U239" t="inlineStr">
         <is>
@@ -35795,12 +35692,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>US-VA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Virginia, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -35825,7 +35722,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>2019-10-05</t>
+          <t>2019-10-12</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -35834,13 +35731,19 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O240" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P240" t="n">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>0</v>
+      </c>
+      <c r="R240" t="n">
+        <v>0.002072293028782716</v>
       </c>
       <c r="U240" t="inlineStr">
         <is>
@@ -35854,7 +35757,7 @@
       </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
@@ -35882,32 +35785,32 @@
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35939,12 +35842,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-FL</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Florida, United States</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -35978,19 +35881,13 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O241" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P241" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
-      <c r="R241" t="n">
-        <v>0.002072293028782716</v>
+        <v>1</v>
       </c>
       <c r="U241" t="inlineStr">
         <is>
@@ -36004,7 +35901,7 @@
       </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
@@ -36032,32 +35929,32 @@
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36089,12 +35986,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>US-FL</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Florida, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -36233,12 +36130,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US-TX</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>Texas, United States</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -36272,13 +36169,13 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O243" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P243" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U243" t="inlineStr">
         <is>
@@ -36377,12 +36274,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>US-TX</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Texas, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -36407,7 +36304,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>2019-10-12</t>
+          <t>2019-10-19</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -36416,13 +36313,19 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O244" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P244" t="n">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>0</v>
+      </c>
+      <c r="R244" t="n">
+        <v>0.0002960418612546737</v>
       </c>
       <c r="U244" t="inlineStr">
         <is>
@@ -36436,7 +36339,7 @@
       </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP244" t="inlineStr">
@@ -36464,32 +36367,32 @@
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36521,12 +36424,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-MO</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Missouri, United States</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -36568,12 +36471,6 @@
       <c r="P245" t="n">
         <v>1</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
-      <c r="R245" t="n">
-        <v>0.0002960418612546737</v>
-      </c>
       <c r="U245" t="inlineStr">
         <is>
           <t>HOLD_US_31b2a115e176e0fae5fc063fe6d1</t>
@@ -36586,7 +36483,7 @@
       </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP245" t="inlineStr">
@@ -36614,32 +36511,32 @@
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36671,12 +36568,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>US-MO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Missouri, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -36701,22 +36598,28 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>2019-10-19</t>
+          <t>2019-11-02</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>2019-10</t>
+          <t>2019-11</t>
         </is>
       </c>
       <c r="N246" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O246" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P246" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>0</v>
+      </c>
+      <c r="R246" t="n">
+        <v>0.001184167445018695</v>
       </c>
       <c r="U246" t="inlineStr">
         <is>
@@ -36730,7 +36633,7 @@
       </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP246" t="inlineStr">
@@ -36758,32 +36661,32 @@
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36815,12 +36718,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-NE</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Nebraska, United States</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -36854,19 +36757,13 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O247" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P247" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
-      <c r="R247" t="n">
-        <v>0.001184167445018695</v>
+        <v>1</v>
       </c>
       <c r="U247" t="inlineStr">
         <is>
@@ -36880,7 +36777,7 @@
       </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
@@ -36908,32 +36805,32 @@
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36965,12 +36862,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>US-NE</t>
+          <t>US-TX</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Nebraska, United States</t>
+          <t>Texas, United States</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -37004,13 +36901,13 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O248" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P248" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U248" t="inlineStr">
         <is>
@@ -37109,12 +37006,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>US-TX</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Texas, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -37139,7 +37036,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>2019-11-02</t>
+          <t>2019-11-09</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -37148,13 +37045,19 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O249" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P249" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>0</v>
+      </c>
+      <c r="R249" t="n">
+        <v>0.0002960418612546737</v>
       </c>
       <c r="U249" t="inlineStr">
         <is>
@@ -37168,7 +37071,7 @@
       </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
@@ -37196,32 +37099,32 @@
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37253,12 +37156,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-TX</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Texas, United States</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -37300,12 +37203,6 @@
       <c r="P250" t="n">
         <v>1</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
-      <c r="R250" t="n">
-        <v>0.0002960418612546737</v>
-      </c>
       <c r="U250" t="inlineStr">
         <is>
           <t>HOLD_US_31b2a115e176e0fae5fc063fe6d1</t>
@@ -37318,7 +37215,7 @@
       </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
@@ -37346,32 +37243,32 @@
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37403,12 +37300,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>US-TX</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Texas, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -37433,7 +37330,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>2019-11-09</t>
+          <t>2019-11-23</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -37442,13 +37339,19 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P251" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>0</v>
+      </c>
+      <c r="R251" t="n">
+        <v>0.0005920837225093475</v>
       </c>
       <c r="U251" t="inlineStr">
         <is>
@@ -37462,7 +37365,7 @@
       </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP251" t="inlineStr">
@@ -37490,32 +37393,32 @@
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37547,12 +37450,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-MD</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Maryland, United States</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -37586,19 +37489,13 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O252" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P252" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
-      <c r="R252" t="n">
-        <v>0.0005920837225093475</v>
+        <v>1</v>
       </c>
       <c r="U252" t="inlineStr">
         <is>
@@ -37612,7 +37509,7 @@
       </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
@@ -37640,32 +37537,32 @@
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37697,12 +37594,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>US-MD</t>
+          <t>US-TX</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Maryland, United States</t>
+          <t>Texas, United States</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -37841,12 +37738,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>US-TX</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Texas, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -37871,7 +37768,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2019-11-23</t>
+          <t>2019-11-30</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -37880,13 +37777,19 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P254" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>0</v>
+      </c>
+      <c r="R254" t="n">
+        <v>0.0005920837225093475</v>
       </c>
       <c r="U254" t="inlineStr">
         <is>
@@ -37900,7 +37803,7 @@
       </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
@@ -37928,32 +37831,32 @@
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37985,12 +37888,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-MD</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Maryland, United States</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -38024,19 +37927,13 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O255" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P255" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
-      <c r="R255" t="n">
-        <v>0.0005920837225093475</v>
+        <v>1</v>
       </c>
       <c r="U255" t="inlineStr">
         <is>
@@ -38050,7 +37947,7 @@
       </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
@@ -38078,32 +37975,32 @@
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38135,12 +38032,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>US-MD</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Maryland, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -38279,12 +38176,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -38309,22 +38206,28 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2019-11-30</t>
+          <t>2019-12-14</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>2019-11</t>
+          <t>2019-12</t>
         </is>
       </c>
       <c r="N257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P257" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>0</v>
+      </c>
+      <c r="R257" t="n">
+        <v>0.0005920837225093475</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
@@ -38338,7 +38241,7 @@
       </c>
       <c r="AO257" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP257" t="inlineStr">
@@ -38366,32 +38269,32 @@
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38423,12 +38326,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -38462,19 +38365,13 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O258" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P258" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
-      <c r="R258" t="n">
-        <v>0.0005920837225093475</v>
+        <v>1</v>
       </c>
       <c r="U258" t="inlineStr">
         <is>
@@ -38488,7 +38385,7 @@
       </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
@@ -38516,32 +38413,32 @@
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38573,12 +38470,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US-OH</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>Ohio, United States</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -38717,12 +38614,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>US-OH</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Ohio, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -38747,7 +38644,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>2019-12-14</t>
+          <t>2019-12-21</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -38764,6 +38661,12 @@
       <c r="P260" t="n">
         <v>1</v>
       </c>
+      <c r="Q260" t="n">
+        <v>0</v>
+      </c>
+      <c r="R260" t="n">
+        <v>0.0002960418612546737</v>
+      </c>
       <c r="U260" t="inlineStr">
         <is>
           <t>HOLD_US_31b2a115e176e0fae5fc063fe6d1</t>
@@ -38776,7 +38679,7 @@
       </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
@@ -38804,32 +38707,32 @@
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38861,12 +38764,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -38908,12 +38811,6 @@
       <c r="P261" t="n">
         <v>1</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
-      <c r="R261" t="n">
-        <v>0.0002960418612546737</v>
-      </c>
       <c r="U261" t="inlineStr">
         <is>
           <t>HOLD_US_31b2a115e176e0fae5fc063fe6d1</t>
@@ -38926,7 +38823,7 @@
       </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
@@ -38954,32 +38851,32 @@
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39011,12 +38908,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -39041,7 +38938,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>2019-12-21</t>
+          <t>2019-12-28</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -39050,13 +38947,19 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O262" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P262" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>0</v>
+      </c>
+      <c r="R262" t="n">
+        <v>0.0008881255837640211</v>
       </c>
       <c r="U262" t="inlineStr">
         <is>
@@ -39070,7 +38973,7 @@
       </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP262" t="inlineStr">
@@ -39098,180 +39001,30 @@
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>D097</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>cyclosporiasis</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>Cyclosporiasis</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>D097</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>Cyclosporiasis</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>环孢子虫病</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>Parasitic</t>
-        </is>
-      </c>
-      <c r="L263" t="inlineStr">
-        <is>
-          <t>2019-12-28</t>
-        </is>
-      </c>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>2019-12</t>
-        </is>
-      </c>
-      <c r="N263" t="n">
-        <v>3</v>
-      </c>
-      <c r="O263" t="n">
-        <v>3</v>
-      </c>
-      <c r="P263" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
-      <c r="R263" t="n">
-        <v>0.0008881255837640211</v>
-      </c>
-      <c r="U263" t="inlineStr">
-        <is>
-          <t>HOLD_US_31b2a115e176e0fae5fc063fe6d1</t>
-        </is>
-      </c>
-      <c r="AA263" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO263" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP263" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS263" t="inlineStr">
-        <is>
-          <t>HOLD_US_31b2a115e176e0fae5fc063fe6d1</t>
-        </is>
-      </c>
-      <c r="AT263" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV263" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW263" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX263" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
-        </is>
-      </c>
-      <c r="AY263" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="AZ263" t="inlineStr">
-        <is>
-          <t>nndss_api; nhss_hiv</t>
-        </is>
-      </c>
-      <c r="BA263" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
-        </is>
-      </c>
-      <c r="BB263" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
-        </is>
-      </c>
-      <c r="BC263" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -39403,7 +39156,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11">
@@ -39423,7 +39176,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -39433,7 +39186,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
